--- a/tabtools/qa/output/tablex_numfmt_t9.xlsx
+++ b/tabtools/qa/output/tablex_numfmt_t9.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="18" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="36" uniqueCount="10">
   <si>
     <t>Percentages</t>
   </si>
@@ -52,10 +52,300 @@
   <numFmts count="1">
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="69">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+  <fonts count="137">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="11"/>
@@ -356,7 +646,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="53">
+  <borders count="105">
     <border>
       <left/>
       <right/>
@@ -704,11 +994,351 @@
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -903,6 +1533,202 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="68" fillId="0" borderId="52" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0"/>
+    <xf numFmtId="166" fontId="69" fillId="0" borderId="57" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="70" fillId="0" borderId="58" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="71" fillId="0" borderId="59" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="60" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="61" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="62" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="63" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="64" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="65" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="66" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="67" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="68" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="69" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="70" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="71" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="72" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="73" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="74" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="75" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="76" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="77" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="78" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="79" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="80" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="81" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="82" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="83" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="84" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="85" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="86" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="87" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="88" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="89" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="90" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="91" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="92" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="93" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="120" fillId="0" borderId="94" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="121" fillId="0" borderId="95" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="122" fillId="0" borderId="96" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="97" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="124" fillId="0" borderId="98" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="0" borderId="99" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="128" fillId="0" borderId="100" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="101" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="132" fillId="0" borderId="102" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="103" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="136" fillId="0" borderId="104" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -918,74 +1744,74 @@
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="2" customWidth="true"/>
-    <col min="2" max="2" width="12.7109375" style="3" customWidth="true"/>
-    <col min="3" max="3" width="15.7109375" style="4" customWidth="true"/>
+    <col min="1" max="1" width="2.7109375" style="54" customWidth="true"/>
+    <col min="2" max="2" width="12.7109375" style="55" customWidth="true"/>
+    <col min="3" max="3" width="15.7109375" style="56" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="20" t="s">
+    <row r="1" s="53" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="72" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="C2" s="92" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="41" t="s">
+      <c r="C3" s="93" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="47" t="s">
+      <c r="B4" s="99" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="48">
+      <c r="C4" s="100">
         <v>70.270270270270274</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="49" t="s">
+      <c r="B5" s="101" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="50">
+      <c r="C5" s="102">
         <v>29.72972972972973</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="51" t="s">
+      <c r="B6" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="52">
+      <c r="C6" s="104">
         <v>100</v>
       </c>
     </row>
